--- a/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语九年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语九年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D263"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1089,6 +1089,16 @@
           <t>happy with</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 乐意</t>
@@ -1101,6 +1111,16 @@
           <t>be happy with</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 对……感到满意；对…满意；高兴</t>
@@ -1113,6 +1133,16 @@
           <t>fill ... with ...</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 充满
@@ -1126,6 +1156,16 @@
           <t>run over</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 轧过；碾过；演练；排练
@@ -1137,6 +1177,16 @@
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>send ... to prison</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1747,6 +1797,16 @@
           <t>sense of humour</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 幽默感；有幽默感；幽默之作</t>
@@ -1759,6 +1819,16 @@
           <t>let ... down</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 使失望；放下；丢面子
@@ -1772,6 +1842,16 @@
           <t>by heart</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 牢记；凭记忆；熟记</t>
@@ -1784,6 +1864,16 @@
           <t>take a seat</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 坐下
@@ -1797,6 +1887,16 @@
           <t>without difficulty</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 容容易易就…
@@ -1810,6 +1910,16 @@
           <t>join in</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 参加；参与
@@ -1823,6 +1933,16 @@
           <t>have no idea</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 心中有数；对…一无所知；感到茫无头绪；不想
@@ -1836,6 +1956,16 @@
           <t>in trouble</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 为难；被捕；未婚怀孕
@@ -1849,6 +1979,16 @@
           <t>be in trouble</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 自讨苦吃；出事
@@ -1862,6 +2002,16 @@
           <t>play a joke on sb.</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 取笑
@@ -1875,6 +2025,16 @@
           <t>turning point</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 转折点；转捩点；转机
@@ -1886,6 +2046,16 @@
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>a series of</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2418,6 +2588,16 @@
           <t>help with</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 帮助
@@ -2431,6 +2611,16 @@
           <t>on business</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因公
@@ -2444,6 +2634,16 @@
           <t>be on business</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -2454,6 +2654,16 @@
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>have no interest in</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3008,6 +3218,16 @@
           <t>on a diet</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 在节食
@@ -3021,6 +3241,16 @@
           <t>be on a diet</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 节食；节食减肥；正在节食</t>
@@ -3033,6 +3263,16 @@
           <t>laugh at</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 嘲笑；付之一笑；因…而发笑
@@ -3046,6 +3286,16 @@
           <t>feel at</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 用手摸着
@@ -3059,6 +3309,16 @@
           <t>feel ashamed of</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 对…感到惭愧；感到羞愧；对……感到羞愧</t>
@@ -3071,6 +3331,16 @@
           <t>drive sb. mad</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
           <t>un. 变疯</t>
@@ -3083,6 +3353,16 @@
           <t>make a mess</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 弄乱；搞成一团糟；搞得乱七八糟</t>
@@ -3095,6 +3375,16 @@
           <t>out of place</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不得其所的；不适当的；不相称的；碍事的
@@ -3108,6 +3398,16 @@
           <t>none of one's business</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3118,6 +3418,16 @@
       <c r="A129" s="2" t="inlineStr">
         <is>
           <t>hear from</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -3673,6 +3983,16 @@
           <t>floor plan</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 楼层平面图
@@ -3686,6 +4006,16 @@
           <t>talent show</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
           <t>n. 业余歌手演唱会; 选秀节目，选秀比赛</t>
@@ -3698,6 +4028,16 @@
           <t>pass out</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 昏倒；分发；主要用于英式英语
@@ -3711,6 +4051,16 @@
           <t>keep still</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 置之不理；不要动；默不作声；忍在肚里
@@ -3724,6 +4074,16 @@
           <t>emergency exit</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 太平门
@@ -3735,6 +4095,16 @@
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>on weekdays</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -4414,6 +4784,16 @@
           <t>a balanced diet</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 均衡饮食
@@ -4427,6 +4807,16 @@
           <t>dairy product</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 乳制品
@@ -4440,6 +4830,16 @@
           <t>stay away from</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 退避三舍；回避；不要到…去；停止和…交往
@@ -4453,6 +4853,16 @@
           <t>fried food</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 油炸食物
@@ -4466,6 +4876,16 @@
           <t>soft drink</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 软饮料（不含酒精）
@@ -4479,6 +4899,16 @@
           <t>medical examination</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 医学检查
@@ -4492,6 +4922,16 @@
           <t>lose weight</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 体重减轻
@@ -4505,6 +4945,16 @@
           <t>plenty of</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 很多的
@@ -4518,6 +4968,16 @@
           <t>in general</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 一般；大体上
@@ -4531,6 +4991,16 @@
           <t>treat oneself to sth.</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
           <t>舍得(吃、穿等)</t>
@@ -4543,6 +5013,16 @@
           <t>prepared to do sth.</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 愿意做</t>
@@ -4553,6 +5033,16 @@
       <c r="A198" s="2" t="inlineStr">
         <is>
           <t>be prepared to do sth.</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -5229,6 +5719,16 @@
           <t>think of</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 想起
@@ -5242,6 +5742,16 @@
           <t>come along</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 进步；同意；一道来；请过来
@@ -5255,6 +5765,16 @@
           <t>what a pity</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 真可惜
@@ -5268,6 +5788,16 @@
           <t>go on doing</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 继续做；继续做原来做的事；继续做同一件事</t>
@@ -5280,6 +5810,16 @@
           <t>in silence</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 沉默着
@@ -5293,6 +5833,16 @@
           <t>after a while</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 过了一会儿
@@ -5306,6 +5856,16 @@
           <t>turn sth. over</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. ￡ 500 a week 每星期卖得五百镑
@@ -5317,6 +5877,16 @@
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>trick sb. into doing sth.</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -5849,6 +6419,16 @@
           <t>at last</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 终于
@@ -5862,6 +6442,16 @@
           <t>fix ... on</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 把…固定住; 把…集中在…上; 确定; 选定</t>
@@ -5874,6 +6464,16 @@
           <t>hold out</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 伸出；提出；维持；制止
@@ -5887,6 +6487,16 @@
           <t>accused of ...</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 被指控犯有……罪；被控犯有…罪；被控告犯有…罪</t>
@@ -5899,6 +6509,16 @@
           <t>be accused of ...</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 被指控；被指责，谴责；被控诉，控告</t>
@@ -5911,6 +6531,16 @@
           <t>under the name ...</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 用……名字</t>
@@ -5921,6 +6551,16 @@
       <c r="A263" s="2" t="inlineStr">
         <is>
           <t>under the name of ...</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
